--- a/public/exports-from-60/11931316.xlsx
+++ b/public/exports-from-60/11931316.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-from-60/11931316.xlsx
+++ b/public/exports-from-60/11931316.xlsx
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejlebrovej 45</t>
+          <t xml:space="preserve">Vejlebrovej 57</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11006,11 +11006,11 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J147">
-        <v>11924</v>
+        <v>650</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -11081,25 +11081,25 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J148">
-        <v>364</v>
+        <v>11924</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873265</t>
+          <t xml:space="preserve">311931691</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-12</t>
+          <t xml:space="preserve">2036-10-14</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejlebrovej 47</t>
+          <t xml:space="preserve">Vejlebrovej 45</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11156,25 +11156,25 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J149">
-        <v>940</v>
+        <v>364</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873265</t>
+          <t xml:space="preserve">311931691</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-12</t>
+          <t xml:space="preserve">2036-10-14</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejlebrovej 57</t>
+          <t xml:space="preserve">Vejlebrovej 47</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11231,25 +11231,25 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J150">
-        <v>650</v>
+        <v>940</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873265</t>
+          <t xml:space="preserve">311931692</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-12</t>
+          <t xml:space="preserve">2036-10-14</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
